--- a/docs/JMeter_Usage_Guide.xlsx
+++ b/docs/JMeter_Usage_Guide.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1321">
   <si>
     <t>JMeter APIテスト 利用方法</t>
   </si>
   <si>
-    <t>対象: Apache JMeter 5.6.3 ／ RHEL 9.8 ／ Windows 11 ／ ツール: jmeter_api_tool v1.0.0（2026-10-25 出力）</t>
+    <t>対象: Apache JMeter 5.6.3 ／ RHEL 9.8 ／ Windows 11 ／ ツール: jmeter_api_tool v1.1.0（2026-10-25 出力）</t>
   </si>
   <si>
     <t>本書は、REST API の定義（URL・HTTPメソッド・クエリパラメータ・ヘッダ・リクエストボディ）を Excel または CSV に記入するか OpenAPI 定義（JSON）を指定して、JMeter のテスト計画ファイル（JMX）を自動生成して実行し、結果を確認するまでの手順をまとめたものです。</t>
@@ -531,7 +531,7 @@
     <t>curl コマンドから API を追加する（add-curl）</t>
   </si>
   <si>
-    <t>ブラウザの開発者ツール（ネットワーク → 右クリック →「Copy as cURL」）や API の仕様書にある curl コマンドを解析して、API一覧に 1 行追加します。Excel は「API一覧」シートの最後の API の次の行（空白行）に、CSV はファイルの末尾に追加します。元のファイルは「ファイル名.日時.bak」に退避してから書き換えます。</t>
+    <t>ブラウザの開発者ツール（ネットワーク → 右クリック →「Copy as cURL」）や API の仕様書にある curl コマンドを解析して、API一覧に追加します（1 コマンド = 1 行。「Copy all as cURL」でコピーした複数のコマンドもまとめて追加できます）。Excel は「API一覧」シートの最後の API の次の行（空白行）に、CSV はファイルの末尾に追加します。元のファイルは「ファイル名.日時.bak」に退避してから書き換えます。</t>
   </si>
   <si>
     <t>./jmeter_api_tool.sh add-curl -i input/api_definition.xlsx --curl-file curl.txt</t>
@@ -573,7 +573,7 @@
     <t>-CurlFile ファイル</t>
   </si>
   <si>
-    <t>curl コマンドを書いたテキストファイル（コピーした内容をそのまま保存したもの。行末の \ ・ ^ ・ ` で改行した複数行のコマンドも可）</t>
+    <t>curl コマンドを書いたテキストファイル（コピーした内容をそのまま保存したもの。行末の \ ・ ^ ・ ` で改行した複数行のコマンド、複数のコマンドも可）</t>
   </si>
   <si>
     <t>--curl "curl …"</t>
@@ -600,7 +600,7 @@
     <t>-ApiName API名</t>
   </si>
   <si>
-    <t>API名（省略時は「メソッド パス」。例: POST /v1/orders）</t>
+    <t>API名（省略時は「メソッド パス」。例: POST /v1/orders。複数のコマンドを追加する場合は、すべての行に同じ API名を設定）</t>
   </si>
   <si>
     <t>--dry-run</t>
@@ -672,10 +672,10 @@
     <t>JMeter の HTTP リクエストに関係しないため無視する（-x プロキシ・--cert など JMeter で別に設定するものは、設定方法を警告で表示して無視）</t>
   </si>
   <si>
-    <t>・1 回に追加するのは 1 行です（&amp;&amp; や ; でつないだ 2 つ目以降のコマンドと、--next 以降は読みません）。</t>
-  </si>
-  <si>
-    <t>・No は既存の No の最大値 + 1、有効は Y、備考は「curl コマンドから追加」です。Excel は書式（罫線・折り返し）を上の行から引き継ぎ、行の高さを内容に合わせます。</t>
+    <t>・複数の curl コマンドを改行・;・&amp;（&amp;&amp; / ||）で区切って並べると、コマンドごとに 1 行ずつ、上から順に追加します（ブラウザの「Copy all as cURL」の bash 形式は ;、cmd 形式は &amp; で区切られています）。| の後ろの jq など curl 以外のコマンドと、--next 以降のリクエストは読みません。</t>
+  </si>
+  <si>
+    <t>・No は既存の No の最大値 + 1 から順に付け、有効は Y、備考は「curl コマンドから追加」です。Excel は書式（罫線・折り返し）を上の行から引き継ぎ、行の高さを内容に合わせます。</t>
   </si>
   <si>
     <t>・CSV は元の文字コード（UTF-8 / UTF-8（BOM 付き）/ Shift_JIS / UTF-16）と改行コードのまま追記します。Shift_JIS で表せない文字を含む場合はエラーになるため、CSV を UTF-8 で保存し直してください。</t>
@@ -822,6 +822,9 @@
     <t>・説明欄の「-J名前」は、実行時に -J名前=値（run コマンドでは -J 名前=値 / -Prop 名前=値）で値を変更できることを表します。</t>
   </si>
   <si>
+    <t>・数値の設定が範囲外の場合（threads・throughput_per_min が 1 未満、loops が -1 未満、それ以外が 0 未満など）と、random_min が random_max より大きい場合は、警告を表示して既定値を使います。</t>
+  </si>
+  <si>
     <t>区分</t>
   </si>
   <si>
@@ -1485,7 +1488,7 @@
     <t>○</t>
   </si>
   <si>
-    <t>HTTP メソッド（GET / POST。PUT / PATCH / DELETE も可）</t>
+    <t>HTTP メソッド（GET / POST / PUT / PATCH / DELETE / HEAD / OPTIONS / TRACE）</t>
   </si>
   <si>
     <t>POST</t>
@@ -1519,7 +1522,7 @@
     <t>ボディ形式</t>
   </si>
   <si>
-    <t>リクエストボディの形式。空欄 = auto（自動判定）</t>
+    <t>リクエストボディの形式（auto / json / form / raw / xml / multipart）。空欄 = auto（自動判定）</t>
   </si>
   <si>
     <t>json</t>
@@ -1528,7 +1531,7 @@
     <t>リクエストボディ</t>
   </si>
   <si>
-    <t>POST 等で送る本文。form 形式は「名前=値」を改行 / &amp; 区切り</t>
+    <t>POST 等で送る本文（前後の空白・改行も含めてそのまま送信）。form / multipart 形式は「名前=値」を改行 / &amp; 区切り</t>
   </si>
   <si>
     <t>{"userId":"${USER_ID}"}</t>
@@ -1621,13 +1624,31 @@
     <t>・「有効」を N にした API は、生成はされますが無効化された状態になります。</t>
   </si>
   <si>
-    <t>・GET / DELETE / OPTIONS のクエリパラメータは HTTP リクエストの「Parameters」タブに設定されます。それ以外（POST / PUT / PATCH / HEAD など）の場合は URL のパスに付与されます（値は UTF-8 で URL エンコード。${...} の部分はそのまま）。</t>
-  </si>
-  <si>
-    <t>・既に URL エンコード済みの値（%E3%83%86 など）は、二重にエンコードしないよう自動で判定します。</t>
-  </si>
-  <si>
-    <t>・GET / DELETE / HEAD / OPTIONS ではリクエストボディは使用できません（指定した場合は警告を表示して無視します）。</t>
+    <t>・GET のクエリパラメータは HTTP リクエストの「Parameters」タブに設定されます。それ以外のメソッドの場合は URL のパスに付与されます（値は UTF-8 で URL エンコード。${...} の部分はそのまま）。JMeter 5.6.3 は DELETE の「Parameters」を URL とボディの両方に送り、HEAD / TRACE の「Parameters」は送らないためです。</t>
+  </si>
+  <si>
+    <t>・URL に書いたクエリ（? 以降）の + は空白として扱います（%20 にして送信）。</t>
+  </si>
+  <si>
+    <t>・名前か値に %XX（%E3%83%86 など）を含む組は URL エンコード済みとして扱い、残りの文字（空白・日本語など）だけをエンコードします（二重にエンコードしません）。%XX を含まない組は JMeter がエンコードします。</t>
+  </si>
+  <si>
+    <t>・multipart のボディは、%XX を元の文字に戻した値をそのまま送信します。</t>
+  </si>
+  <si>
+    <t>・リクエストボディは記入したとおり（前後の空白・改行を含めて）送信します。空白だけのセルは空欄として扱います。</t>
+  </si>
+  <si>
+    <t>・GET / DELETE / HEAD / OPTIONS / TRACE ではリクエストボディは使用できません（指定した場合は警告を表示して無視します）。</t>
+  </si>
+  <si>
+    <t>・URL は http / https（${PROTOCOL} のような変数も可）とホスト名が必要です。ホスト名が無い・ポート番号が 1～65535 でないなど、正しくない URL の API は警告を表示してスキップします。URL の「ユーザー名:パスワード@」は送信されないため、警告を表示して取り除きます（Basic 認証はヘッダに Authorization: Basic … を記入してください）。</t>
+  </si>
+  <si>
+    <t>・ヘッダに Cookie を書いた場合、クッキー管理（設定 cookie_manager）が有効でその URL へ送るクッキー（設定 cookies・応答の Set-Cookie）があると、JMeter はヘッダの Cookie をそのクッキーで置き換えます（生成時に警告を表示します）。クッキーは設定 cookies に記入してください。</t>
+  </si>
+  <si>
+    <t>・CSV の引用符（"）が閉じられていない場合や、Excel の「API一覧」「設定」シートに計算結果の無い数式・エラー値（#N/A など）のセルがある場合は、値が欠けたまま生成しないようエラーにします。</t>
   </si>
   <si>
     <t>ボディ形式（auto の場合の自動判定）</t>
@@ -1675,6 +1696,9 @@
     <t>本文をそのまま送信（Content-Type はヘッダ列で指定）</t>
   </si>
   <si>
+    <t>・ボディ形式は auto のほか、json / form / raw / xml（本文をそのまま送信。Content-Type が未指定なら application/xml を付与）/ multipart（名前=値 を multipart/form-data のテキスト項目として送信）を指定できます。</t>
+  </si>
+  <si>
     <t>generate コマンドの -i に OpenAPI 3.0.x の定義ファイル（JSON、拡張子 .json）を指定すると、定義の各操作（パスとメソッドの組）を「API一覧」と同じ 1行 = 1API に変換してから JMX を生成します。API は定義に書かれた順番に実行されます。</t>
   </si>
   <si>
@@ -1717,7 +1741,7 @@
     <t>-AnyMethod メソッド</t>
   </si>
   <si>
-    <t>x-amazon-apigateway-any-method（ANY）の API で送るメソッド（GET / POST / PUT / PATCH / DELETE / HEAD / OPTIONS。既定: GET）</t>
+    <t>x-amazon-apigateway-any-method（ANY）の API で送るメソッド（GET / POST / PUT / PATCH / DELETE / HEAD / OPTIONS / TRACE。既定: GET）</t>
   </si>
   <si>
     <t>--required-only</t>
@@ -1726,7 +1750,7 @@
     <t>-RequiredOnly</t>
   </si>
   <si>
-    <t>必須（required）のパラメータ・プロパティだけを生成</t>
+    <t>必須（required）のパラメータ・プロパティ・リクエストボディだけを生成</t>
   </si>
   <si>
     <t>--use-examples</t>
@@ -1771,10 +1795,10 @@
     <t>メソッド / URL</t>
   </si>
   <si>
-    <t>操作のメソッドとパス。パスパラメータはデータ型に合ったランダム値（URL エンコード済み）。接続先とパスの先頭は設定 base_url</t>
-  </si>
-  <si>
-    <t>in: query のパラメータ（style / explode に従って展開）</t>
+    <t>操作のメソッドとパス。パスパラメータはデータ型に合ったランダム値（style: simple / label / matrix と explode に従い、区切り文字以外を URL エンコード）。接続先とパスの先頭は設定 base_url（operation / path に servers がある場合はその接続先）</t>
+  </si>
+  <si>
+    <t>in: query のパラメータ（style / explode に従って展開。explode しない配列・オブジェクトと spaceDelimited / pipeDelimited は、各値を URL エンコードしてから区切り文字でつなぐ。content で定義したパラメータは JSON などの文字列）</t>
   </si>
   <si>
     <t>Content-Type（リクエストボディの形式）、Accept（成功応答の形式）、in: header / in: cookie のパラメータ、OpenAPI 用設定 API_HEADERS の値（同じ名前のヘッダは API_HEADERS の値を使用）</t>
@@ -1783,7 +1807,7 @@
     <t>ボディ形式 / リクエストボディ</t>
   </si>
   <si>
-    <t>requestBody の定義から生成（JSON → json、application/x-www-form-urlencoded → form、multipart/form-data → multipart、XML・テキストなど → raw）</t>
+    <t>requestBody の定義から生成（JSON → json、application/x-www-form-urlencoded → form（encoding の style / explode に対応）、multipart/form-data → multipart、XML → xml、テキストなど → raw）</t>
   </si>
   <si>
     <t>2xx の応答コード（カンマ区切り。2XX だけの場合は空欄）</t>
@@ -1801,7 +1825,13 @@
     <t>・認証ヘッダ（Authorization・API-Key）はランダム値では通らないため、OpenAPI 定義のパラメータからは生成しません。Authorization は設定 common_headers、または OpenAPI 用設定ファイルの HEADERS / TOKEN_DIR で、API-Key は API_HEADERS で指定します（API_HEADERS の既定値の API-Key: XXXXXXX は実際のキーに書き換えてください）。指定が無い場合は生成時に警告を表示します。</t>
   </si>
   <si>
-    <t>・GET / DELETE / HEAD / OPTIONS のリクエストボディは、Excel / CSV と同じ規則で送信しません（警告を表示します）。</t>
+    <t>・GET / DELETE / HEAD / OPTIONS / TRACE のリクエストボディは、Excel / CSV と同じ規則で送信しません（警告を表示します）。</t>
+  </si>
+  <si>
+    <t>・operation または path に servers がある場合は、その servers[0].url をその API の接続先にします（相対 URL はドキュメントの接続先のホストを使います）。設定ファイル（-s）で base_url を指定した場合は、すべての API をその接続先に送ります。OpenAPI 用設定の PROTOCOL / HOST / PORT は operation / path の servers にも反映します。</t>
+  </si>
+  <si>
+    <t>・in: cookie のパラメータはヘッダ Cookie に設定します。クッキー管理（設定 cookie_manager）が有効でクッキーがあると JMeter が置き換えるため、生成時に警告を表示します。</t>
   </si>
   <si>
     <t>・設定ファイルで空欄の base_url（servers[0].url。無い場合は http://localhost:8080）・test_plan_name（「タイトル APIのバージョン（OpenAPI のバージョン）」）・output_file（「タイトル.jmx」）は OpenAPI 定義の値を使います（output_file は -n / -JmxName が優先）。</t>
@@ -1825,7 +1855,7 @@
     <t>プロトコル</t>
   </si>
   <si>
-    <t>共通変数 PROTOCOL の既定値（http / https）。空欄 = OpenAPI 定義（servers[0].url）または設定 base_url の値。実行時は -JPROTOCOL=値 で変更できます</t>
+    <t>共通変数 PROTOCOL の既定値（http / https）。空欄 = OpenAPI 定義（servers[0].url）または設定 base_url の値。記入した値は operation / path の servers の接続先にも使います。実行時は -JPROTOCOL=値 で変更できます</t>
   </si>
   <si>
     <t>HOST</t>
@@ -1834,7 +1864,7 @@
     <t>ホスト名</t>
   </si>
   <si>
-    <t>共通変数 HOST の既定値（例: api.example.com）。空欄 = OpenAPI 定義（servers[0].url）または設定 base_url の値。実行時は -JHOST=値 で変更できます</t>
+    <t>共通変数 HOST の既定値（例: api.example.com）。空欄 = OpenAPI 定義（servers[0].url）または設定 base_url の値。記入した値は operation / path の servers の接続先にも使います。実行時は -JHOST=値 で変更できます</t>
   </si>
   <si>
     <t>PORT</t>
@@ -1843,7 +1873,7 @@
     <t>ポート番号</t>
   </si>
   <si>
-    <t>共通変数 PORT の既定値（1～65535）。空欄 = 未設定（ポート番号なし。http は 80 / https は 443 で接続）。PROTOCOL と HOST も空欄の場合は OpenAPI 定義（servers[0].url）または設定 base_url の値。実行時は -JPORT=値 で変更できます</t>
+    <t>共通変数 PORT の既定値（1～65535）。空欄 = 未設定（ポート番号なし。http は 80 / https は 443 で接続）。PROTOCOL と HOST も空欄の場合は OpenAPI 定義（servers[0].url）または設定 base_url の値。記入した値は operation / path の servers の接続先にも使います。実行時は -JPORT=値 で変更できます</t>
   </si>
   <si>
     <t>HTTPヘッダ</t>
@@ -1901,7 +1931,7 @@
     <t>OpenAPI 定義（info.title）のプレースホルダ ${name_prefix} に入れる値（例: dev）。テストプラン名と出力する JMX のファイル名に使われます。空欄 = 未設定（${name_prefix} を隣の区切り文字（- _ . / 空白）ごと取り除きます。例: ${name_prefix}-api → api）</t>
   </si>
   <si>
-    <t>・PROTOCOL / HOST / PORT は、記入した項目だけ base_url の接続先を置き換え、パス（例: /v1）はそのまま使います。PORT が空欄の場合はポート番号を付けません（http は 80 / https は 443 で接続）。実行時の -JPROTOCOL= / -JHOST= / -JPORT= も使えます。</t>
+    <t>・PROTOCOL / HOST / PORT は、記入した項目だけ base_url と operation / path の servers の接続先を置き換え、パス（例: /v1）はそのまま使います。PORT が空欄の場合はポート番号を付けません（http は 80 / https は 443 で接続）。実行時の -JPROTOCOL= / -JHOST= / -JPORT= も使えます。</t>
   </si>
   <si>
     <t>・API_HEADERS の値は各 API のヘッダ（API ごとの HTTP Header Manager）の初期値です。生成後は JMeter で API ごとに変更でき、HEADERS（共通ヘッダ）と同じ名前のヘッダは実行時に API 側が優先されます。</t>
@@ -2120,10 +2150,10 @@
     <t>[任意] Excelデータ読込</t>
   </si>
   <si>
-    <t>Excel（.xlsx）をメモリに読み込む（Apache POI 不要）</t>
-  </si>
-  <si>
-    <t>Excel の値が変数に設定されない</t>
+    <t>Excel（.xlsx）をメモリに読み込む（Apache POI 不要）。読み込めない場合は失敗として記録し、テストを停止する</t>
+  </si>
+  <si>
+    <t>Excel の値が変数に設定されない（「Excelデータ行取得」も無効化・削除する）</t>
   </si>
   <si>
     <t>[必須] メイン処理</t>
@@ -2435,6 +2465,12 @@
     <t>・CSV データ読込は、ファイルが見つからないとスレッドがエラーで停止します。CSV を使わない場合は削除してください。</t>
   </si>
   <si>
+    <t>・Excel データ読込は、ファイル・シート・データ行が無い場合や、計算結果の無い数式・エラー値のセルがある場合に、失敗として JTL・レポートに記録してテストを停止します（値の無い変数で API を呼び出さないため）。Excel を使わない場合は「Excelデータ読込」と「Excelデータ行取得」を無効化・削除するか、設定 excel_data を OFF にして生成してください。実行時だけ使わない場合は -JEXCEL_FILE=（空）を指定します。</t>
+  </si>
+  <si>
+    <t>・アクセストークン読込は、ファイルの読み込みに失敗した場合（他のプロセスが書き込み中など）、前回読み込んだトークンを使い、次の API の呼び出しで読み直します。</t>
+  </si>
+  <si>
     <t>・生成時に設定を OFF にすると、その要素は最初から生成されません（「4.入力項目_設定」参照）。</t>
   </si>
   <si>
@@ -2480,7 +2516,7 @@
     <t>・-i・-s・-c・--seed など入力に関するオプションは、JMX を生成するときと同じです。-o・-n は使いません（指定しても無視します）。--split とは同時に指定できません。</t>
   </si>
   <si>
-    <t>・更新前の JMX は「JMX名.jmx.日時.bak」に退避します。更新した後は、基準ファイル（JMX名.jmx.base.json）と Linux サーバでの実行コマンド（JMX名_linux_cmd.txt）も作り直します。</t>
+    <t>・更新前の JMX は「JMX名.jmx.日時.bak」に退避します（同じ秒に退避したファイルがある場合は「日時_2」のように連番を付けます）。更新後の JMX を書き終えてから置き換えるため、書き込みに失敗しても元の JMX は残ります。更新した後は、基準ファイル（JMX名.jmx.base.json）と Linux サーバでの実行コマンド（JMX名_linux_cmd.txt）も作り直します。</t>
   </si>
   <si>
     <t>・違う箇所が無い場合は、JMX を書き換えません。</t>
@@ -2585,7 +2621,7 @@
     <t>・基準ファイルが無い場合（ファイルを削除した場合や、基準ファイルを作らない以前の版で生成した JMX）は、現在の JMX と今回の定義を直接比べ、違う箇所を定義の内容に更新します。JMeter で変更した値も定義の値に戻り、JMeter で削除した要素も追加し直すため（JMeter で追加した要素と、共通のスクリプトの変更は残します）、先に --dry-run / -DryRun で確認してください。1 回更新すると基準ファイルが作られ、次からは JMeter の変更を残す比較になります。</t>
   </si>
   <si>
-    <t>・OpenAPI 定義の場合は、同じ API名の API の番号（APIxx）を引き継ぎ、追加された API には既存の番号の続きを付けます。基準ファイルがあれば、操作の定義（パラメータ・リクエストボディ・参照先のスキーマ）が変わっていない API は前回と同じテストデータを使います。乱数シードは前回の値（基準ファイル、無ければ JMX のコメントに書かれた値）を使います（--seed / -Seed で変更できます）。</t>
+    <t>・OpenAPI 定義の場合は、同じ API名の API の番号（APIxx）を引き継ぎ、追加された API には既存の番号の続きを付けます。基準ファイルがあれば、操作の定義（パラメータ・リクエストボディ・参照先のスキーマ）が変わっていない API は前回と同じテストデータを使います。乱数シードは前回の値（基準ファイル、無ければ JMX のコメントに書かれた値）を使います（--seed / -Seed で変更できます）。v1.1.0 で OpenAPI 定義から作る行の形式（パス・クエリの style など）を変えたため、v1.0.0 の基準ファイルを使う最初の更新では、すべての API の行を前回と同じ乱数シードで作り直します（定義が同じならテストデータの値は同じで、変わった形式の箇所だけが [変更] になります）。</t>
   </si>
   <si>
     <t>実行モードの使い分け</t>
@@ -3683,13 +3719,40 @@
     <t>jmeter.log を確認。jmeter -g result.jtl -o 新しいフォルダ で再作成</t>
   </si>
   <si>
-    <t>Excel のデータが読み込まれない</t>
-  </si>
-  <si>
-    <t>ファイルパス・シート名の誤り、.xls 形式</t>
-  </si>
-  <si>
-    <t>jmeter.log の [Excel] の行を確認。.xlsx 形式で保存する（.xls は非対応）</t>
+    <t>Excel のデータが読み込まれない・「Excelデータ読込」が失敗してテストが止まる</t>
+  </si>
+  <si>
+    <t>ファイルパス・シート名の誤り、.xls 形式、データ行が無い、計算結果の無い数式</t>
+  </si>
+  <si>
+    <t>jmeter.log の [Excel] の行を確認。.xlsx 形式で保存する（.xls は非対応）。Excel を使わない場合は「Excelデータ読込」「Excelデータ行取得」を無効化する</t>
+  </si>
+  <si>
+    <t>ヘッダに書いた Cookie が送信されない</t>
+  </si>
+  <si>
+    <t>クッキー管理（Cookie Manager）がクッキーを持っているとヘッダの Cookie を置き換える</t>
+  </si>
+  <si>
+    <t>クッキーは設定 cookies に記入するか、設定 cookie_manager を OFF にする</t>
+  </si>
+  <si>
+    <t>引用符（"）が閉じられていません（generate）</t>
+  </si>
+  <si>
+    <t>CSV のセルの " の対応が取れていない</t>
+  </si>
+  <si>
+    <t>エラーの行を確認し、値を "..." で囲み、値の中の " は "" と書く</t>
+  </si>
+  <si>
+    <t>読み取れないセルがあります（generate）</t>
+  </si>
+  <si>
+    <t>Excel のセルが計算結果の無い数式・エラー値</t>
+  </si>
+  <si>
+    <t>Excel で開いて数式の結果を確認し、保存し直す</t>
   </si>
   <si>
     <t>JSON の構文エラーです（YAML 形式は未対応です）（generate）</t>
@@ -3791,7 +3854,7 @@
     <t>jmeter_api_tool.bat add-curl -i API一覧 (-CurlFile ファイル / -Curl "curl …") [-ApiName API名] [-DryRun]</t>
   </si>
   <si>
-    <t>curl コマンドを解析して API一覧に 1 行追加（「3.JMX生成」参照）</t>
+    <t>curl コマンドを解析して API一覧に追加（1 コマンド = 1 行。複数のコマンドも可。「3.JMX生成」参照）</t>
   </si>
   <si>
     <t>linux-cmd</t>
@@ -4576,7 +4639,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -4584,42 +4647,42 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4627,7 +4690,7 @@
     <row r="11" ht="4" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="6" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -4642,42 +4705,42 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="11" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -4692,21 +4755,21 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="11" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -4725,68 +4788,68 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -4797,58 +4860,58 @@
         <v>229</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
     </row>
     <row r="36" ht="32.4" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="15" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
     </row>
     <row r="38" ht="32.4" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -4856,10 +4919,10 @@
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="13" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>176</v>
@@ -4867,152 +4930,152 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="14" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="15" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
     </row>
     <row r="50" ht="32.4" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
     </row>
     <row r="57" ht="6" customHeight="1"/>
     <row r="58" ht="8" customHeight="1"/>
     <row r="59" ht="24" customHeight="1">
       <c r="B59" s="4" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -5020,7 +5083,7 @@
     <row r="60" ht="4" customHeight="1"/>
     <row r="61" ht="32.4" customHeight="1">
       <c r="B61" s="6" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -5028,28 +5091,28 @@
     <row r="62" ht="6" customHeight="1"/>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="7" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="7" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -5057,7 +5120,7 @@
     <row r="67" ht="6" customHeight="1"/>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="6" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -5065,7 +5128,7 @@
     <row r="69" ht="6" customHeight="1"/>
     <row r="70" ht="16.2" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
@@ -5073,7 +5136,7 @@
     <row r="71" ht="6" customHeight="1"/>
     <row r="72" ht="16.2" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="12"/>
@@ -5092,13 +5155,13 @@
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -5109,20 +5172,20 @@
         <v>229</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
     </row>
     <row r="77" ht="6" customHeight="1"/>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="7" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="7" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -5131,7 +5194,7 @@
     <row r="81" ht="8" customHeight="1"/>
     <row r="82" ht="24" customHeight="1">
       <c r="B82" s="4" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -5139,21 +5202,21 @@
     <row r="83" ht="4" customHeight="1"/>
     <row r="84" ht="16.2" customHeight="1">
       <c r="B84" s="9" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
     </row>
     <row r="85" ht="16.2" customHeight="1">
       <c r="B85" s="10" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
     </row>
     <row r="86" ht="16.2" customHeight="1">
       <c r="B86" s="11" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
@@ -5168,7 +5231,7 @@
     </row>
     <row r="89" ht="30.6" customHeight="1">
       <c r="B89" s="11" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
@@ -5176,14 +5239,14 @@
     <row r="90" ht="6" customHeight="1"/>
     <row r="91" ht="18" customHeight="1">
       <c r="B91" s="7" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -5192,7 +5255,7 @@
     <row r="94" ht="8" customHeight="1"/>
     <row r="95" ht="24" customHeight="1">
       <c r="B95" s="4" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -5200,21 +5263,21 @@
     <row r="96" ht="4" customHeight="1"/>
     <row r="97" ht="18" customHeight="1">
       <c r="B97" s="7" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="B98" s="7" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="B99" s="7" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -5294,7 +5357,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -5302,7 +5365,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -5310,75 +5373,75 @@
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="13" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="8" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -5386,49 +5449,49 @@
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="7" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="7" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="7" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -5437,7 +5500,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -5445,53 +5508,53 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
     <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="B34" s="4" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -5499,35 +5562,35 @@
     <row r="35" ht="4" customHeight="1"/>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="9" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -5536,7 +5599,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -5544,21 +5607,21 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="7" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -5567,7 +5630,7 @@
     <row r="49" ht="8" customHeight="1"/>
     <row r="50" ht="24" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -5575,7 +5638,7 @@
     <row r="51" ht="4" customHeight="1"/>
     <row r="52" ht="46.8" customHeight="1">
       <c r="B52" s="6" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -5638,50 +5701,50 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="C5" s="9"/>
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="11" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="C11" s="11"/>
     </row>
@@ -5689,55 +5752,55 @@
     <row r="13" ht="8" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" ht="4" customHeight="1"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="C22" s="6"/>
     </row>
@@ -5745,14 +5808,14 @@
     <row r="24" ht="8" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="4" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="C25" s="4"/>
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>6</v>
@@ -5760,74 +5823,74 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="14" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="15" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="14" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -5835,29 +5898,29 @@
         <v>197</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="14" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="8" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="C41" s="4"/>
     </row>
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="46.8" customHeight="1">
       <c r="B43" s="6" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="C43" s="6"/>
     </row>
@@ -5865,14 +5928,14 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="C46" s="4"/>
     </row>
     <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="32.4" customHeight="1">
       <c r="B48" s="6" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="C48" s="6"/>
     </row>
@@ -5880,26 +5943,26 @@
     <row r="50" ht="8" customHeight="1"/>
     <row r="51" ht="24" customHeight="1">
       <c r="B51" s="4" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="C51" s="4"/>
     </row>
     <row r="52" ht="4" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="7" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="C55" s="7"/>
     </row>
@@ -5959,7 +6022,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -5967,10 +6030,10 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>6</v>
@@ -5978,97 +6041,97 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -6076,152 +6139,152 @@
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="14" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="14" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="14" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>1118</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="14" t="s">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>1120</v>
+        <v>1132</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>1121</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>1122</v>
+        <v>1134</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>1124</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="24" customHeight="1">
       <c r="B33" s="4" t="s">
-        <v>1125</v>
+        <v>1137</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -6229,21 +6292,21 @@
     <row r="34" ht="4" customHeight="1"/>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="9" t="s">
-        <v>1126</v>
+        <v>1138</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>1128</v>
+        <v>1140</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -6257,21 +6320,21 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="10" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="16.2" customHeight="1">
       <c r="B41" s="10" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -6285,28 +6348,28 @@
     </row>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="10" t="s">
-        <v>1132</v>
+        <v>1144</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>1133</v>
+        <v>1145</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
     <row r="45" ht="16.2" customHeight="1">
       <c r="B45" s="10" t="s">
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
     </row>
     <row r="46" ht="16.2" customHeight="1">
       <c r="B46" s="10" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
@@ -6320,14 +6383,14 @@
     </row>
     <row r="48" ht="16.2" customHeight="1">
       <c r="B48" s="10" t="s">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
     </row>
     <row r="49" ht="16.2" customHeight="1">
       <c r="B49" s="11" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -6335,21 +6398,21 @@
     <row r="50" ht="6" customHeight="1"/>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="7" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -6358,7 +6421,7 @@
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
       <c r="B56" s="4" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -6366,60 +6429,60 @@
     <row r="57" ht="4" customHeight="1"/>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>1142</v>
+        <v>1154</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>1143</v>
+        <v>1155</v>
       </c>
       <c r="D58" s="13"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="14" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>1145</v>
+        <v>1157</v>
       </c>
       <c r="D59" s="14"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="15" t="s">
-        <v>1146</v>
+        <v>1158</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="D60" s="15"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>1148</v>
+        <v>1160</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
       <c r="D61" s="14"/>
     </row>
     <row r="62" ht="32.4" customHeight="1">
       <c r="B62" s="15" t="s">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>1151</v>
+        <v>1163</v>
       </c>
       <c r="D62" s="15"/>
     </row>
     <row r="63" ht="6" customHeight="1"/>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>1152</v>
+        <v>1164</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -6428,7 +6491,7 @@
     <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="24" customHeight="1">
       <c r="B68" s="4" t="s">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -6436,55 +6499,55 @@
     <row r="69" ht="4" customHeight="1"/>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="13" t="s">
-        <v>1142</v>
+        <v>1154</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="D70" s="13"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="14" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="D71" s="14"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="15" t="s">
-        <v>1158</v>
+        <v>1170</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="D72" s="15"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="14" t="s">
-        <v>1160</v>
+        <v>1172</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="D73" s="14"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="15" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>1163</v>
+        <v>1175</v>
       </c>
       <c r="D74" s="15"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
       <c r="D75" s="14"/>
     </row>
@@ -6542,7 +6605,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6561,269 +6624,302 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>1166</v>
+        <v>1178</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>1169</v>
+        <v>1181</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="15" t="s">
-        <v>1172</v>
+        <v>1184</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="7" ht="32.4" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1184</v>
+        <v>1196</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1185</v>
+        <v>1197</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1189</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>1190</v>
+        <v>1202</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1191</v>
+        <v>1203</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1192</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1194</v>
+        <v>1206</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="13" ht="32.4" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>1196</v>
+        <v>1208</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1198</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1200</v>
+        <v>1212</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="17" ht="32.4" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>1208</v>
+        <v>1220</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="19" ht="32.4" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="20" ht="32.4" customHeight="1">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="20" ht="46.8" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="21" ht="32.4" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="22" ht="32.4" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="23" ht="46.8" customHeight="1">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="24" ht="32.4" customHeight="1">
       <c r="B24" s="14" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="25" ht="32.4" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="26" ht="32.4" customHeight="1">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="26" ht="46.8" customHeight="1">
       <c r="B26" s="14" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="27" ht="32.4" customHeight="1">
+      <c r="B27" s="15" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="28" ht="32.4" customHeight="1">
+      <c r="B28" s="14" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="29" ht="32.4" customHeight="1">
+      <c r="B29" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
@@ -6862,7 +6958,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>1238</v>
+        <v>1259</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -6871,13 +6967,13 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>1239</v>
+        <v>1260</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1240</v>
+        <v>1261</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1241</v>
+        <v>1262</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>176</v>
@@ -6885,107 +6981,107 @@
     </row>
     <row r="6" ht="32.4" customHeight="1">
       <c r="B6" s="14" t="s">
-        <v>1242</v>
+        <v>1263</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1243</v>
+        <v>1264</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1244</v>
+        <v>1265</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1245</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="7" ht="61.2" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>1246</v>
+        <v>1267</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1249</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8" ht="46.8" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1253</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="9" ht="32.4" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>1254</v>
+        <v>1275</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1255</v>
+        <v>1276</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1256</v>
+        <v>1277</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1257</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
       <c r="B10" s="14" t="s">
-        <v>1258</v>
+        <v>1279</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1259</v>
+        <v>1280</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1260</v>
+        <v>1281</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1261</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>1262</v>
+        <v>1283</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1263</v>
+        <v>1284</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1264</v>
+        <v>1285</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1265</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>1266</v>
+        <v>1287</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>147</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1267</v>
+        <v>1288</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1268</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="8" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>1269</v>
+        <v>1290</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -6994,7 +7090,7 @@
     <row r="16" ht="4" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="13" t="s">
-        <v>1270</v>
+        <v>1291</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>176</v>
@@ -7004,50 +7100,50 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>1271</v>
+        <v>1292</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1272</v>
+        <v>1293</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>1274</v>
+        <v>1295</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1275</v>
+        <v>1296</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>1276</v>
+        <v>1297</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>1278</v>
+        <v>1299</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1279</v>
+        <v>1300</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
@@ -7057,7 +7153,7 @@
         <v>228</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1280</v>
+        <v>1301</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -7067,97 +7163,97 @@
         <v>237</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>1282</v>
+        <v>1303</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="14" t="s">
-        <v>1284</v>
+        <v>1305</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1285</v>
+        <v>1306</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1287</v>
+        <v>1308</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="14" t="s">
-        <v>1288</v>
+        <v>1309</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1289</v>
+        <v>1310</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>1290</v>
+        <v>1311</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>1291</v>
+        <v>1312</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="14" t="s">
-        <v>1292</v>
+        <v>1313</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1293</v>
+        <v>1314</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="15" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>1295</v>
+        <v>1316</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="14" t="s">
-        <v>1296</v>
+        <v>1317</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="s">
-        <v>1298</v>
+        <v>1319</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>1299</v>
+        <v>1320</v>
       </c>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
@@ -8102,7 +8198,7 @@
       <c r="D27" s="4"/>
     </row>
     <row r="28" ht="4" customHeight="1"/>
-    <row r="29" ht="32.4" customHeight="1">
+    <row r="29" ht="46.8" customHeight="1">
       <c r="B29" s="6" t="s">
         <v>168</v>
       </c>
@@ -8209,7 +8305,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="32.4" customHeight="1">
       <c r="B44" s="14" t="s">
         <v>189</v>
       </c>
@@ -8323,14 +8419,14 @@
       <c r="D56" s="14"/>
     </row>
     <row r="57" ht="6" customHeight="1"/>
-    <row r="58" ht="18" customHeight="1">
+    <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
     </row>
-    <row r="59" ht="18" customHeight="1">
+    <row r="59" ht="32.4" customHeight="1">
       <c r="B59" s="7" t="s">
         <v>216</v>
       </c>
@@ -8690,7 +8786,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -8739,1020 +8835,1030 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" ht="6" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="13" t="s">
+    <row r="7" ht="32.4" customHeight="1">
+      <c r="B7" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="C9" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="E9" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="14" t="s">
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="D10" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="E10" s="14" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="F10" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="D10" s="15" t="s">
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="D11" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="E11" s="15" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="11" ht="32.4" customHeight="1">
-      <c r="B11" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="F11" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="D11" s="14" t="s">
+    </row>
+    <row r="12" ht="32.4" customHeight="1">
+      <c r="B12" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="E12" s="14" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" s="15" t="s">
+      <c r="F12" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="15" t="s">
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="D13" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="14" t="s">
+      <c r="F13" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="C13" s="14" t="s">
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="C14" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="D14" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="F14" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="D14" s="15" t="s">
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="D15" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="15" ht="32.4" customHeight="1">
-      <c r="B15" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="F15" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="D15" s="14" t="s">
+    </row>
+    <row r="16" ht="32.4" customHeight="1">
+      <c r="B16" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="D16" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="E16" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="16" ht="32.4" customHeight="1">
-      <c r="B16" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="F16" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="D16" s="15" t="s">
+    </row>
+    <row r="17" ht="32.4" customHeight="1">
+      <c r="B17" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F16" s="15" t="s">
+      <c r="D17" s="15" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="17" ht="32.4" customHeight="1">
-      <c r="B17" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="E17" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="D17" s="14" t="s">
+    </row>
+    <row r="18" ht="32.4" customHeight="1">
+      <c r="B18" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="D18" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="E18" s="14" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="15" t="s">
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="D19" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="E19" s="15" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="F19" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="D19" s="14" t="s">
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="E20" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="15" t="s">
+      <c r="F20" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="C20" s="15" t="s">
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="C21" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="D21" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="E21" s="15" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="F21" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="D21" s="14" t="s">
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="D22" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="E22" s="14" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="D22" s="15" t="s">
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="D23" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="E23" s="15" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="23" ht="46.8" customHeight="1">
-      <c r="B23" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="F23" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="D23" s="14" t="s">
+    </row>
+    <row r="24" ht="46.8" customHeight="1">
+      <c r="B24" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F23" s="14" t="s">
+      <c r="D24" s="14" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="24" ht="75.6" customHeight="1">
-      <c r="B24" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C24" s="15" t="s">
+      <c r="E24" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="D24" s="15" t="s">
+    </row>
+    <row r="25" ht="75.6" customHeight="1">
+      <c r="B25" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F24" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="25" ht="61.2" customHeight="1">
-      <c r="B25" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C25" s="14" t="s">
+      <c r="E25" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="D25" s="14" t="s">
+    </row>
+    <row r="26" ht="61.2" customHeight="1">
+      <c r="B26" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="E26" s="14" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C26" s="15" t="s">
+      <c r="F26" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D26" s="15" t="s">
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="D27" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="E27" s="15" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C27" s="14" t="s">
+      <c r="F27" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="D27" s="14" t="s">
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="F27" s="14" t="s">
+      <c r="D28" s="14" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="E28" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D28" s="15" t="s">
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="D29" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="E29" s="15" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="14" t="s">
+      <c r="F29" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C29" s="14" t="s">
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="C30" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F29" s="14" t="s">
+      <c r="D30" s="14" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C30" s="15" t="s">
+      <c r="E30" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="D30" s="15" t="s">
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="F30" s="15" t="s">
+      <c r="D31" s="15" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="31" ht="32.4" customHeight="1">
-      <c r="B31" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="C31" s="14" t="s">
+      <c r="E31" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="D31" s="14" t="s">
+    </row>
+    <row r="32" ht="32.4" customHeight="1">
+      <c r="B32" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F31" s="14" t="s">
+      <c r="D32" s="14" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C32" s="15" t="s">
+      <c r="E32" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="F32" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="D32" s="15" t="s">
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F32" s="15" t="s">
+      <c r="D33" s="15" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="33" ht="32.4" customHeight="1">
-      <c r="B33" s="14" t="s">
+      <c r="E33" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F33" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C33" s="14" t="s">
+    </row>
+    <row r="34" ht="32.4" customHeight="1">
+      <c r="B34" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="C34" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="E33" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F33" s="14" t="s">
+      <c r="D34" s="14" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C34" s="15" t="s">
+      <c r="E34" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="F34" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D34" s="15" t="s">
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F34" s="15" t="s">
+      <c r="D35" s="15" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="C35" s="14" t="s">
+      <c r="E35" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F35" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="D35" s="14" t="s">
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="D36" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="E36" s="14" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="F36" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="D36" s="15" t="s">
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="D37" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="E37" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="15"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="D37" s="14" t="s">
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="D38" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="E38" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="14"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="D38" s="15" t="s">
+      <c r="F38" s="14"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="D39" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="E39" s="15" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="F39" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="D39" s="14" t="s">
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="D40" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="E40" s="14" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="F40" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="D40" s="15" t="s">
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="E40" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F40" s="15" t="s">
+      <c r="D41" s="15" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="E41" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F41" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="D41" s="14" t="s">
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C42" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="D42" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="F41" s="14"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="C42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="F42" s="14"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="D43" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="15"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="D43" s="14" t="s">
+      <c r="F43" s="15"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C44" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="D44" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="F43" s="14"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="15" t="s">
+      <c r="E44" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="F44" s="14"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="C45" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="E44" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F44" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="45" ht="32.4" customHeight="1">
-      <c r="B45" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="C45" s="14" t="s">
+      <c r="E45" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F45" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="D45" s="14" t="s">
+    </row>
+    <row r="46" ht="32.4" customHeight="1">
+      <c r="B46" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="D46" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="E46" s="14" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="B46" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C46" s="15" t="s">
+      <c r="F46" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="D46" s="15" t="s">
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="E46" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F46" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="E47" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F47" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="D47" s="14" t="s">
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="E47" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="F47" s="14"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="B48" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C48" s="15" t="s">
+      <c r="D48" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="E48" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="F48" s="14"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="D49" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="F48" s="15"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="C49" s="14" t="s">
+      <c r="E49" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="F49" s="15"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C50" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="F49" s="14" t="s">
+      <c r="D50" s="14" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C50" s="15" t="s">
+      <c r="E50" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="F50" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D50" s="15" t="s">
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="E50" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="F50" s="15" t="s">
+      <c r="D51" s="15" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="51" ht="32.4" customHeight="1">
-      <c r="B51" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="C51" s="14" t="s">
+      <c r="E51" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="F51" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="D51" s="14" t="s">
+    </row>
+    <row r="52" ht="32.4" customHeight="1">
+      <c r="B52" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="D52" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="E52" s="14" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="15" t="s">
+      <c r="F52" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="C52" s="15" t="s">
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="C53" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F52" s="15" t="s">
+      <c r="D53" s="15" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="53" ht="32.4" customHeight="1">
-      <c r="B53" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="C53" s="14" t="s">
+      <c r="E53" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F53" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="D53" s="14" t="s">
+    </row>
+    <row r="54" ht="32.4" customHeight="1">
+      <c r="B54" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="D54" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="E54" s="14" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="C54" s="15" t="s">
+      <c r="F54" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="D54" s="15" t="s">
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="E54" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F54" s="15" t="s">
+      <c r="D55" s="15" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="14" t="s">
+      <c r="E55" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F55" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="C55" s="14" t="s">
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="s">
         <v>430</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="C56" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="E55" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F55" s="14" t="s">
+      <c r="D56" s="14" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="56" ht="32.4" customHeight="1">
-      <c r="B56" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="C56" s="15" t="s">
+      <c r="E56" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F56" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="D56" s="15" t="s">
+    </row>
+    <row r="57" ht="32.4" customHeight="1">
+      <c r="B57" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="E56" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F56" s="15" t="s">
+      <c r="D57" s="15" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="57" ht="32.4" customHeight="1">
-      <c r="B57" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="C57" s="14" t="s">
+      <c r="E57" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F57" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="D57" s="14" t="s">
+    </row>
+    <row r="58" ht="32.4" customHeight="1">
+      <c r="B58" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="C58" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="E57" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F57" s="14" t="s">
+      <c r="D58" s="14" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="58" ht="32.4" customHeight="1">
-      <c r="B58" s="15" t="s">
+      <c r="E58" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F58" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C58" s="15" t="s">
+    </row>
+    <row r="59" ht="32.4" customHeight="1">
+      <c r="B59" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="C59" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="D59" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="E59" s="15" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C59" s="14" t="s">
+      <c r="F59" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="D59" s="14" t="s">
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C60" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="E59" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F59" s="14" t="s">
+      <c r="D60" s="14" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C60" s="15" t="s">
+      <c r="E60" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F60" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="D60" s="15" t="s">
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C61" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="E60" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F60" s="15" t="s">
+      <c r="D61" s="15" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="B61" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C61" s="14" t="s">
+      <c r="E61" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F61" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="D61" s="14" t="s">
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C62" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="E61" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F61" s="14" t="s">
+      <c r="D62" s="14" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C62" s="15" t="s">
+      <c r="E62" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F62" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="D62" s="15" t="s">
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="E62" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F62" s="15" t="s">
+      <c r="D63" s="15" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="B63" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C63" s="14" t="s">
+      <c r="E63" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F63" s="15" t="s">
         <v>456</v>
       </c>
-      <c r="D63" s="14" t="s">
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C64" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="E63" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F63" s="14" t="s">
+      <c r="D64" s="14" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="B64" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C64" s="15" t="s">
+      <c r="E64" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F64" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="D64" s="15" t="s">
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C65" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="E64" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F64" s="15" t="s">
+      <c r="D65" s="15" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="B65" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C65" s="14" t="s">
+      <c r="E65" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F65" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="D65" s="14" t="s">
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C66" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="D66" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="E66" s="14" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C66" s="15" t="s">
+      <c r="F66" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="D66" s="15" t="s">
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C67" s="15" t="s">
         <v>467</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="D67" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="F66" s="15" t="s">
+      <c r="E67" s="15" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="B67" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C67" s="14" t="s">
+      <c r="F67" s="15" t="s">
         <v>470</v>
       </c>
-      <c r="D67" s="14" t="s">
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C68" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="E67" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="F67" s="14" t="s">
+      <c r="D68" s="14" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="68" ht="6" customHeight="1"/>
+      <c r="E68" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="69" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -9767,7 +9873,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -9788,7 +9894,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -9797,16 +9903,16 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>176</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" ht="32.4" customHeight="1">
@@ -9815,7 +9921,7 @@
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>7</v>
@@ -9823,40 +9929,40 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="15" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="9" ht="32.4" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" ht="32.4" customHeight="1">
@@ -9864,157 +9970,157 @@
         <v>197</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" ht="32.4" customHeight="1">
       <c r="B11" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="B12" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" ht="32.4" customHeight="1">
       <c r="B13" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14" ht="32.4" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" ht="32.4" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" ht="32.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="22" ht="32.4" customHeight="1">
       <c r="B22" s="14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -10023,7 +10129,7 @@
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -10031,7 +10137,7 @@
     <row r="25" ht="8" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -10040,7 +10146,7 @@
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="32.4" customHeight="1">
       <c r="B28" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -10048,7 +10154,7 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -10056,7 +10162,7 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -10064,7 +10170,7 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -10072,7 +10178,7 @@
     </row>
     <row r="32" ht="32.4" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -10080,94 +10186,151 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="32.4" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
     </row>
-    <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" ht="4" customHeight="1"/>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="13" t="s">
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="E39" s="13"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="14" t="s">
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" ht="32.4" customHeight="1">
+      <c r="B38" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="D40" s="14" t="s">
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" ht="32.4" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="E40" s="14"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="15" t="s">
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" ht="32.4" customHeight="1">
+      <c r="B40" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="24" customHeight="1">
+      <c r="B43" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" ht="4" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="E41" s="15"/>
-    </row>
-    <row r="42" ht="32.4" customHeight="1">
-      <c r="B42" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="E45" s="13"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="E42" s="14"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="15" t="s">
+      <c r="C46" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="D46" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="E46" s="14"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="C47" s="15" t="s">
         <v>548</v>
       </c>
-      <c r="E43" s="15"/>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
+      <c r="D47" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="E47" s="15"/>
+    </row>
+    <row r="48" ht="32.4" customHeight="1">
+      <c r="B48" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="E48" s="14"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="E49" s="15"/>
+    </row>
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="32.4" customHeight="1">
+      <c r="B51" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="23">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B26:E26"/>
@@ -10178,12 +10341,19 @@
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="B37:E37"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="B51:E51"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -10198,7 +10368,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -10221,7 +10391,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="32.4" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -10232,7 +10402,7 @@
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="24" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -10251,7 +10421,7 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -10260,7 +10430,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="11" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -10279,7 +10449,7 @@
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -10288,7 +10458,7 @@
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="11" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -10311,78 +10481,78 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
     </row>
     <row r="18" ht="32.4" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
     </row>
     <row r="19" ht="32.4" customHeight="1">
       <c r="B19" s="14" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="14" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
@@ -10390,7 +10560,7 @@
     <row r="23" ht="6" customHeight="1"/>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="7" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -10399,7 +10569,7 @@
     </row>
     <row r="25" ht="32.4" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -10410,7 +10580,7 @@
     <row r="27" ht="8" customHeight="1"/>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -10420,10 +10590,10 @@
     <row r="29" ht="4" customHeight="1"/>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -10431,32 +10601,32 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="14" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="32.4" customHeight="1">
       <c r="B32" s="15" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="32.4" customHeight="1">
       <c r="B33" s="14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
@@ -10464,21 +10634,21 @@
     </row>
     <row r="34" ht="32.4" customHeight="1">
       <c r="B34" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
     </row>
-    <row r="35" ht="18" customHeight="1">
+    <row r="35" ht="32.4" customHeight="1">
       <c r="B35" s="14" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
@@ -10486,10 +10656,10 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
@@ -10500,7 +10670,7 @@
         <v>98</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
@@ -10509,7 +10679,7 @@
     <row r="38" ht="6" customHeight="1"/>
     <row r="39" ht="32.4" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -10518,7 +10688,7 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="7" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -10527,7 +10697,7 @@
     </row>
     <row r="41" ht="32.4" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -10536,7 +10706,7 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="7" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -10545,110 +10715,94 @@
     </row>
     <row r="43" ht="32.4" customHeight="1">
       <c r="B43" s="7" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" ht="32.4" customHeight="1">
+    <row r="44" ht="18" customHeight="1">
       <c r="B44" s="7" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" ht="6" customHeight="1"/>
-    <row r="46" ht="8" customHeight="1"/>
-    <row r="47" ht="24" customHeight="1">
-      <c r="B47" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-    </row>
-    <row r="48" ht="4" customHeight="1"/>
-    <row r="49" ht="32.4" customHeight="1">
-      <c r="B49" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="18" customHeight="1">
-      <c r="B51" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C51" s="13" t="s">
+    <row r="45" ht="32.4" customHeight="1">
+      <c r="B45" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" ht="32.4" customHeight="1">
+      <c r="B46" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" ht="6" customHeight="1"/>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="24" customHeight="1">
+      <c r="B49" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" ht="4" customHeight="1"/>
+    <row r="51" ht="32.4" customHeight="1">
+      <c r="B51" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" ht="6" customHeight="1"/>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="C53" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="D53" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="E53" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" s="13" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="52" ht="46.8" customHeight="1">
-      <c r="B52" s="14" t="s">
-        <v>596</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>598</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="53" ht="46.8" customHeight="1">
-      <c r="B53" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="54" ht="61.2" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="55" ht="46.8" customHeight="1">
@@ -10656,108 +10810,124 @@
         <v>606</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="56" ht="90" customHeight="1">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="56" ht="75.6" customHeight="1">
       <c r="B56" s="14" t="s">
         <v>606</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>611</v>
+        <v>281</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="57" ht="118.8" customHeight="1">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="57" ht="46.8" customHeight="1">
       <c r="B57" s="15" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>328</v>
+        <v>616</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="58" ht="61.2" customHeight="1">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="58" ht="90" customHeight="1">
       <c r="B58" s="14" t="s">
         <v>616</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>280</v>
+        <v>621</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="59" ht="61.2" customHeight="1">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="59" ht="118.8" customHeight="1">
       <c r="B59" s="15" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>621</v>
+        <v>329</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="32.4" customHeight="1">
-      <c r="B61" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-    </row>
-    <row r="62" ht="32.4" customHeight="1">
-      <c r="B62" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-    </row>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="60" ht="61.2" customHeight="1">
+      <c r="B60" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="61" ht="61.2" customHeight="1">
+      <c r="B61" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1"/>
     <row r="63" ht="32.4" customHeight="1">
       <c r="B63" s="7" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -10766,7 +10936,7 @@
     </row>
     <row r="64" ht="32.4" customHeight="1">
       <c r="B64" s="7" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -10775,25 +10945,43 @@
     </row>
     <row r="65" ht="32.4" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
     </row>
-    <row r="66" ht="46.8" customHeight="1">
+    <row r="66" ht="32.4" customHeight="1">
       <c r="B66" s="7" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
     </row>
-    <row r="67" ht="6" customHeight="1"/>
+    <row r="67" ht="32.4" customHeight="1">
+      <c r="B67" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" ht="46.8" customHeight="1">
+      <c r="B68" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="43">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
@@ -10827,14 +11015,16 @@
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -10849,7 +11039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -10870,7 +11060,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -10879,7 +11069,7 @@
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="16.2" customHeight="1">
       <c r="B5" s="9" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -10887,7 +11077,7 @@
     </row>
     <row r="6" ht="16.2" customHeight="1">
       <c r="B6" s="10" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -10895,7 +11085,7 @@
     </row>
     <row r="7" ht="16.2" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -10903,7 +11093,7 @@
     </row>
     <row r="8" ht="16.2" customHeight="1">
       <c r="B8" s="10" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -10911,7 +11101,7 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -10919,7 +11109,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -10927,7 +11117,7 @@
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="10" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -10935,7 +11125,7 @@
     </row>
     <row r="12" ht="16.2" customHeight="1">
       <c r="B12" s="10" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -10943,7 +11133,7 @@
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -10951,7 +11141,7 @@
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="10" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -10959,7 +11149,7 @@
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="B15" s="10" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -10967,7 +11157,7 @@
     </row>
     <row r="16" ht="16.2" customHeight="1">
       <c r="B16" s="10" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -10975,7 +11165,7 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -10983,7 +11173,7 @@
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -10991,7 +11181,7 @@
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="10" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -10999,7 +11189,7 @@
     </row>
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="10" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -11007,7 +11197,7 @@
     </row>
     <row r="21" ht="16.2" customHeight="1">
       <c r="B21" s="10" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -11015,7 +11205,7 @@
     </row>
     <row r="22" ht="16.2" customHeight="1">
       <c r="B22" s="10" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -11023,7 +11213,7 @@
     </row>
     <row r="23" ht="16.2" customHeight="1">
       <c r="B23" s="10" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -11031,7 +11221,7 @@
     </row>
     <row r="24" ht="16.2" customHeight="1">
       <c r="B24" s="10" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -11039,7 +11229,7 @@
     </row>
     <row r="25" ht="16.2" customHeight="1">
       <c r="B25" s="10" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -11047,7 +11237,7 @@
     </row>
     <row r="26" ht="16.2" customHeight="1">
       <c r="B26" s="10" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -11055,7 +11245,7 @@
     </row>
     <row r="27" ht="16.2" customHeight="1">
       <c r="B27" s="10" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -11063,7 +11253,7 @@
     </row>
     <row r="28" ht="16.2" customHeight="1">
       <c r="B28" s="10" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -11071,7 +11261,7 @@
     </row>
     <row r="29" ht="16.2" customHeight="1">
       <c r="B29" s="10" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -11079,7 +11269,7 @@
     </row>
     <row r="30" ht="16.2" customHeight="1">
       <c r="B30" s="10" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -11087,7 +11277,7 @@
     </row>
     <row r="31" ht="16.2" customHeight="1">
       <c r="B31" s="10" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -11095,7 +11285,7 @@
     </row>
     <row r="32" ht="16.2" customHeight="1">
       <c r="B32" s="10" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -11103,7 +11293,7 @@
     </row>
     <row r="33" ht="16.2" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -11111,7 +11301,7 @@
     </row>
     <row r="34" ht="16.2" customHeight="1">
       <c r="B34" s="10" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -11119,7 +11309,7 @@
     </row>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -11127,7 +11317,7 @@
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -11135,7 +11325,7 @@
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -11143,7 +11333,7 @@
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -11151,7 +11341,7 @@
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
@@ -11159,7 +11349,7 @@
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="11" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -11169,7 +11359,7 @@
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="4" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -11178,401 +11368,401 @@
     <row r="44" ht="4" customHeight="1"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="46" ht="32.4" customHeight="1">
       <c r="B46" s="14" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
     </row>
     <row r="47" ht="32.4" customHeight="1">
       <c r="B47" s="15" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="52" ht="32.4" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
     </row>
     <row r="53" ht="32.4" customHeight="1">
       <c r="B53" s="15" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="14" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="15" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="14" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="15" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="14" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
     </row>
     <row r="59" ht="32.4" customHeight="1">
       <c r="B59" s="15" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
     </row>
     <row r="60" ht="32.4" customHeight="1">
       <c r="B60" s="14" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="15" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="14" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="15" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="64" ht="32.4" customHeight="1">
       <c r="B64" s="14" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
     </row>
     <row r="65" ht="32.4" customHeight="1">
       <c r="B65" s="15" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
     </row>
     <row r="66" ht="32.4" customHeight="1">
       <c r="B66" s="14" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="15" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="68" ht="32.4" customHeight="1">
       <c r="B68" s="14" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
     </row>
     <row r="69" ht="32.4" customHeight="1">
       <c r="B69" s="15" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
     </row>
     <row r="70" ht="32.4" customHeight="1">
       <c r="B70" s="14" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
     </row>
     <row r="71" ht="32.4" customHeight="1">
       <c r="B71" s="15" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="14" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>771</v>
+        <v>781</v>
       </c>
     </row>
     <row r="73" ht="6" customHeight="1"/>
     <row r="74" ht="8" customHeight="1"/>
     <row r="75" ht="24" customHeight="1">
       <c r="B75" s="4" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -11581,133 +11771,133 @@
     <row r="76" ht="4" customHeight="1"/>
     <row r="77" ht="18" customHeight="1">
       <c r="B77" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="E77" s="13"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="14" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="E78" s="14"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>777</v>
+        <v>787</v>
       </c>
       <c r="E79" s="15"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="E80" s="14"/>
     </row>
     <row r="81" ht="32.4" customHeight="1">
       <c r="B81" s="15" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="E81" s="15"/>
     </row>
     <row r="82" ht="32.4" customHeight="1">
       <c r="B82" s="14" t="s">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="E82" s="14"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="15" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="E83" s="15"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="14" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="E84" s="14"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="15" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="E85" s="15"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="14" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="E86" s="14"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="15" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="E87" s="15"/>
     </row>
@@ -11715,7 +11905,7 @@
     <row r="89" ht="8" customHeight="1"/>
     <row r="90" ht="24" customHeight="1">
       <c r="B90" s="4" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -11724,7 +11914,7 @@
     <row r="91" ht="4" customHeight="1"/>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="7" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -11732,7 +11922,7 @@
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -11740,23 +11930,39 @@
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="B94" s="7" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
     </row>
-    <row r="95" ht="18" customHeight="1">
+    <row r="95" ht="46.8" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
     </row>
-    <row r="96" ht="6" customHeight="1"/>
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+    </row>
+    <row r="98" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="58">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
@@ -11813,6 +12019,8 @@
     <mergeCell ref="B93:E93"/>
     <mergeCell ref="B94:E94"/>
     <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B97:E97"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -11846,7 +12054,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="46.8" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -11855,7 +12063,7 @@
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="24" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -11870,42 +12078,42 @@
     </row>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="10" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="10" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
     </row>
     <row r="11" ht="16.2" customHeight="1">
       <c r="B11" s="10" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
     <row r="12" ht="16.2" customHeight="1">
       <c r="B12" s="10" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="B13" s="10" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="B14" s="11" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -11920,21 +12128,21 @@
     </row>
     <row r="17" ht="16.2" customHeight="1">
       <c r="B17" s="10" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="16.2" customHeight="1">
       <c r="B18" s="10" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="16.2" customHeight="1">
       <c r="B19" s="11" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -11959,7 +12167,7 @@
         <v>241</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -11970,27 +12178,27 @@
         <v>193</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
     </row>
     <row r="24" ht="6" customHeight="1"/>
     <row r="25" ht="32.4" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" ht="32.4" customHeight="1">
+    <row r="26" ht="46.8" customHeight="1">
       <c r="B26" s="7" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="7" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -11999,7 +12207,7 @@
     <row r="29" ht="8" customHeight="1"/>
     <row r="30" ht="24" customHeight="1">
       <c r="B30" s="4" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -12007,98 +12215,98 @@
     <row r="31" ht="4" customHeight="1"/>
     <row r="32" ht="16.2" customHeight="1">
       <c r="B32" s="9" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
     </row>
     <row r="33" ht="16.2" customHeight="1">
       <c r="B33" s="10" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
     </row>
     <row r="34" ht="16.2" customHeight="1">
       <c r="B34" s="10" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
     </row>
     <row r="35" ht="16.2" customHeight="1">
       <c r="B35" s="10" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
     </row>
     <row r="36" ht="16.2" customHeight="1">
       <c r="B36" s="10" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" ht="16.2" customHeight="1">
       <c r="B37" s="10" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="16.2" customHeight="1">
       <c r="B38" s="10" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="16.2" customHeight="1">
       <c r="B39" s="10" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="16.2" customHeight="1">
       <c r="B40" s="10" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="16.2" customHeight="1">
       <c r="B41" s="10" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="16.2" customHeight="1">
       <c r="B42" s="10" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="16.2" customHeight="1">
       <c r="B43" s="10" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
     <row r="44" ht="16.2" customHeight="1">
       <c r="B44" s="10" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
     <row r="45" ht="30.6" customHeight="1">
       <c r="B45" s="11" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
@@ -12106,7 +12314,7 @@
     <row r="46" ht="6" customHeight="1"/>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="13" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>6</v>
@@ -12115,46 +12323,46 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="D48" s="14"/>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="15" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="D49" s="15"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="14" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="D50" s="14"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="15" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="D51" s="15"/>
     </row>
     <row r="52" ht="32.4" customHeight="1">
       <c r="B52" s="14" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D52" s="14"/>
     </row>
@@ -12162,7 +12370,7 @@
     <row r="54" ht="8" customHeight="1"/>
     <row r="55" ht="24" customHeight="1">
       <c r="B55" s="4" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -12170,49 +12378,49 @@
     <row r="56" ht="4" customHeight="1"/>
     <row r="57" ht="32.4" customHeight="1">
       <c r="B57" s="7" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
     <row r="58" ht="32.4" customHeight="1">
       <c r="B58" s="7" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
     </row>
     <row r="59" ht="46.8" customHeight="1">
       <c r="B59" s="7" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="7" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="7" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
     </row>
     <row r="62" ht="61.2" customHeight="1">
       <c r="B62" s="7" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
     </row>
-    <row r="63" ht="46.8" customHeight="1">
+    <row r="63" ht="75.6" customHeight="1">
       <c r="B63" s="7" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
